--- a/05-06-26/shakoor sb.xlsx
+++ b/05-06-26/shakoor sb.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC11FD4-A5CF-40C8-A51D-920AB9EDFB3B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B470B7-9016-4C94-85F2-798B5AA082FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -32,14 +32,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1858,167 +1850,167 @@
     <xf numFmtId="43" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2129,7 +2121,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Cust. Price List"/>
@@ -2891,9 +2883,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2931,9 +2923,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2966,26 +2958,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3018,26 +2993,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3345,30 +3303,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>7</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -3379,24 +3337,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -3407,45 +3365,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -3456,17 +3414,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -3477,32 +3435,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -3510,7 +3468,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="169">
@@ -3519,16 +3477,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -3536,7 +3494,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -3546,21 +3504,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -3572,14 +3530,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -3587,7 +3545,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -3599,11 +3557,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -3644,9 +3602,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -4201,14 +4159,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -4275,104 +4233,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -4387,39 +4345,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -4434,10 +4392,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -4447,55 +4405,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -4507,6 +4429,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0900-000000000000}">
@@ -4564,30 +4522,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>8</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -4598,24 +4556,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -4626,45 +4584,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -4675,17 +4633,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -4696,32 +4654,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -4729,23 +4687,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -4753,7 +4711,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>50</v>
       </c>
@@ -4763,21 +4721,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -4789,14 +4747,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -4804,7 +4762,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -4816,11 +4774,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -4861,9 +4819,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -5418,14 +5376,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -5492,104 +5450,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -5604,39 +5562,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -5651,10 +5609,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -5664,55 +5622,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -5724,6 +5646,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0A00-000000000000}">
@@ -5781,30 +5739,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>9</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -5815,24 +5773,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -5843,45 +5801,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -5892,17 +5850,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -5913,32 +5871,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -5946,23 +5904,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="167"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -5970,7 +5928,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -5980,21 +5938,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -6006,14 +5964,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -6021,7 +5979,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -6033,11 +5991,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -6078,9 +6036,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -6635,14 +6593,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -6709,104 +6667,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -6821,39 +6779,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -6868,10 +6826,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -6881,55 +6839,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -6941,6 +6863,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0B00-000000000000}">
@@ -6998,30 +6956,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>10</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -7032,24 +6990,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -7060,45 +7018,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -7109,17 +7067,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -7130,32 +7088,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -7163,23 +7121,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -7187,7 +7145,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -7197,21 +7155,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -7223,14 +7181,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -7238,7 +7196,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -7250,11 +7208,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -7295,9 +7253,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -7852,14 +7810,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -7926,104 +7884,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -8038,39 +7996,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -8085,10 +8043,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -8098,55 +8056,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -8158,6 +8080,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0C00-000000000000}">
@@ -8215,30 +8173,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>10</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -8249,24 +8207,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -8277,45 +8235,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -8326,17 +8284,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -8347,32 +8305,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -8380,23 +8338,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -8404,7 +8362,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>50</v>
       </c>
@@ -8414,21 +8372,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -8440,14 +8398,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -8455,7 +8413,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -8467,11 +8425,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -8512,9 +8470,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -9069,14 +9027,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -9143,104 +9101,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -9255,39 +9213,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -9302,10 +9260,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -9315,55 +9273,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -9375,6 +9297,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0D00-000000000000}">
@@ -9432,30 +9390,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>10</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -9466,24 +9424,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -9494,45 +9452,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -9543,17 +9501,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -9564,32 +9522,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -9597,7 +9555,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -9606,16 +9564,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -9623,7 +9581,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -9633,21 +9591,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -9659,14 +9617,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -9674,7 +9632,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64" t="s">
         <v>101</v>
       </c>
@@ -9688,11 +9646,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -9733,9 +9691,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -10290,14 +10248,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -10364,104 +10322,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -10476,39 +10434,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -10523,10 +10481,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -10536,55 +10494,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -10596,6 +10518,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0E00-000000000000}">
@@ -13405,30 +13363,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>1</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -13439,24 +13397,24 @@
       </c>
     </row>
     <row r="4" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -13467,43 +13425,43 @@
       </c>
     </row>
     <row r="5" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="201" t="s">
+      <c r="A5" s="241" t="s">
         <v>119</v>
       </c>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
+      <c r="B5" s="241"/>
+      <c r="C5" s="241"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="201"/>
-      <c r="B6" s="201"/>
-      <c r="C6" s="201"/>
+      <c r="A6" s="241"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -13514,17 +13472,17 @@
       </c>
     </row>
     <row r="7" spans="1:21 16383:16384" s="73" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -13535,32 +13493,32 @@
       </c>
     </row>
     <row r="8" spans="1:21 16383:16384" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:21 16383:16384" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -13568,21 +13526,21 @@
       </c>
     </row>
     <row r="10" spans="1:21 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203"/>
+      <c r="A10" s="224"/>
       <c r="B10" s="75"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -13590,67 +13548,67 @@
       </c>
     </row>
     <row r="11" spans="1:21 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76"/>
       <c r="C11" s="77"/>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:21 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203"/>
+      <c r="A12" s="224"/>
       <c r="B12" s="76"/>
       <c r="C12" s="77"/>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
-      <c r="T12" s="212" t="s">
+      <c r="T12" s="196" t="s">
         <v>106</v>
       </c>
-      <c r="U12" s="213"/>
+      <c r="U12" s="197"/>
       <c r="XFD12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:21 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
       <c r="L13" s="79">
         <v>0.05</v>
       </c>
-      <c r="T13" s="214"/>
-      <c r="U13" s="215"/>
+      <c r="T13" s="198"/>
+      <c r="U13" s="199"/>
       <c r="XFD13" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:21 16383:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -13662,19 +13620,19 @@
       <c r="F14" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="206" t="s">
+      <c r="G14" s="234" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="207"/>
-      <c r="I14" s="207" t="s">
+      <c r="H14" s="235"/>
+      <c r="I14" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="207" t="s">
+      <c r="J14" s="235" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="207"/>
-      <c r="L14" s="209"/>
-      <c r="M14" s="210" t="s">
+      <c r="K14" s="235"/>
+      <c r="L14" s="237"/>
+      <c r="M14" s="229" t="s">
         <v>71</v>
       </c>
       <c r="N14" s="83" t="s">
@@ -13699,9 +13657,9 @@
       </c>
     </row>
     <row r="15" spans="1:21 16383:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -13717,7 +13675,7 @@
       <c r="H15" s="171" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="208"/>
+      <c r="I15" s="236"/>
       <c r="J15" s="171" t="s">
         <v>78</v>
       </c>
@@ -13727,7 +13685,7 @@
       <c r="L15" s="174" t="s">
         <v>80</v>
       </c>
-      <c r="M15" s="211"/>
+      <c r="M15" s="231"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -14390,14 +14348,14 @@
       </c>
     </row>
     <row r="25" spans="1:21 16384:16384" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="218"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="202"/>
       <c r="G25" s="176">
         <f t="shared" ref="G25:M25" si="3">SUM(G16:G24)</f>
         <v>0</v>
@@ -14482,104 +14440,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:21 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>547222.19999999995</v>
       </c>
     </row>
     <row r="29" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>91526.543999999994</v>
       </c>
     </row>
     <row r="30" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>455695.65599999996</v>
       </c>
     </row>
     <row r="32" spans="1:21 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -14594,39 +14552,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>537720.87407999998</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -14641,10 +14599,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>551163.89593200001</v>
@@ -14654,19 +14612,50 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
     <mergeCell ref="T12:U13"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
@@ -14683,37 +14672,6 @@
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -14771,30 +14729,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>1</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -14805,24 +14763,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -14833,45 +14791,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>119</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -14882,17 +14840,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -14903,32 +14861,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -14936,7 +14894,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -14945,16 +14903,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -14962,7 +14920,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -14972,21 +14930,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -14998,14 +14956,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -15013,7 +14971,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="168">
         <v>3520247902365</v>
       </c>
@@ -15027,11 +14985,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -15072,9 +15030,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -15645,14 +15603,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -15719,104 +15677,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>116224.2</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>13946.903999999999</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>102277.296</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -15831,39 +15789,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>120687.20928000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -15878,10 +15836,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>121290.64532640002</v>
@@ -15891,19 +15849,55 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -15915,42 +15909,6 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -16008,30 +15966,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>2</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -16042,24 +16000,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -16070,45 +16028,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>119</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -16119,17 +16077,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -16140,32 +16098,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -16173,7 +16131,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -16182,16 +16140,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -16199,7 +16157,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -16209,21 +16167,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -16235,14 +16193,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -16250,7 +16208,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="168">
         <v>300426949714</v>
       </c>
@@ -16264,11 +16222,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -16309,9 +16267,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -16882,14 +16840,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="8">SUM(G16:G24)</f>
         <v>0</v>
@@ -16956,104 +16914,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>430998</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>77579.64</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>353418.36</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -17068,39 +17026,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>417033.66479999997</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -17115,10 +17073,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>419118.833124</v>
@@ -17128,55 +17086,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -17188,6 +17110,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -17245,30 +17203,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>4</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -17279,24 +17237,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -17307,45 +17265,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -17356,17 +17314,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -17377,32 +17335,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -17410,23 +17368,23 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="169"/>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -17434,7 +17392,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>50</v>
       </c>
@@ -17444,21 +17402,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -17470,14 +17428,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -17485,7 +17443,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="56"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -17497,11 +17455,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -17542,9 +17500,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -18099,14 +18057,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -18173,104 +18131,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -18285,39 +18243,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -18332,10 +18290,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -18345,55 +18303,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -18405,6 +18327,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -18461,30 +18419,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>3</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -18495,24 +18453,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -18523,45 +18481,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -18572,17 +18530,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -18593,32 +18551,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -18626,7 +18584,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -18635,16 +18593,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -18652,7 +18610,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -18662,21 +18620,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -18688,14 +18646,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -18703,7 +18661,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -18715,11 +18673,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -18760,9 +18718,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -19317,14 +19275,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -19391,104 +19349,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -19503,39 +19461,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -19550,10 +19508,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -19563,55 +19521,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -19623,6 +19545,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -19680,30 +19638,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>5</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -19714,24 +19672,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -19742,45 +19700,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -19791,17 +19749,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -19812,32 +19770,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -19845,7 +19803,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="169" t="s">
@@ -19854,16 +19812,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -19871,7 +19829,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -19881,21 +19839,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -19907,14 +19865,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -19922,7 +19880,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -19934,11 +19892,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -19979,9 +19937,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -20536,14 +20494,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -20610,104 +20568,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -20722,39 +20680,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -20769,10 +20727,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -20782,55 +20740,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -20842,6 +20764,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -20899,30 +20857,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="242" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
     </row>
     <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="227" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
+      <c r="B3" s="227"/>
+      <c r="C3" s="227"/>
       <c r="F3" s="70"/>
       <c r="G3" s="71"/>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="226" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="197">
+      <c r="L3" s="226"/>
+      <c r="M3" s="226"/>
+      <c r="N3" s="227">
         <v>6</v>
       </c>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="O3" s="227"/>
+      <c r="P3" s="227"/>
       <c r="R3" s="70"/>
       <c r="S3" s="71"/>
       <c r="XFC3" t="s">
@@ -20933,24 +20891,24 @@
       </c>
     </row>
     <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
       <c r="F4" s="70"/>
       <c r="G4" s="71"/>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199">
+      <c r="L4" s="226"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="240">
         <f ca="1">TODAY()</f>
-        <v>46184</v>
-      </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="199"/>
+        <v>46188</v>
+      </c>
+      <c r="O4" s="240"/>
+      <c r="P4" s="240"/>
       <c r="R4" s="70"/>
       <c r="S4" s="71"/>
       <c r="XFC4" s="73" t="s">
@@ -20961,45 +20919,45 @@
       </c>
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="249" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
       <c r="F5" s="70"/>
       <c r="G5" s="71"/>
-      <c r="K5" s="198" t="s">
+      <c r="K5" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="199">
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="240">
         <f ca="1">N4-1</f>
-        <v>46183</v>
-      </c>
-      <c r="O5" s="197"/>
-      <c r="P5" s="197"/>
+        <v>46187</v>
+      </c>
+      <c r="O5" s="227"/>
+      <c r="P5" s="227"/>
       <c r="R5" s="70"/>
       <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="198" t="s">
+      <c r="A6" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="F6" s="70"/>
       <c r="G6" s="74"/>
-      <c r="K6" s="198" t="s">
+      <c r="K6" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="200" t="s">
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="239" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="200"/>
-      <c r="P6" s="200"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
       <c r="R6" s="70"/>
       <c r="S6" s="74"/>
       <c r="XFC6" t="s">
@@ -21010,17 +20968,17 @@
       </c>
     </row>
     <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="198"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
       <c r="F7" s="70"/>
       <c r="G7" s="74"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="200"/>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
       <c r="R7" s="70"/>
       <c r="S7" s="74"/>
       <c r="XFC7" t="s">
@@ -21031,32 +20989,32 @@
       </c>
     </row>
     <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="202"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="238"/>
+      <c r="C8" s="238"/>
       <c r="F8" s="70"/>
       <c r="G8" s="74"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="200"/>
-      <c r="O8" s="200"/>
-      <c r="P8" s="200"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="239"/>
       <c r="R8" s="70"/>
       <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="202"/>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
       <c r="F9" s="70"/>
       <c r="G9" s="74"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="200"/>
-      <c r="O9" s="200"/>
-      <c r="P9" s="200"/>
+      <c r="K9" s="226"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="239"/>
       <c r="R9" s="70"/>
       <c r="S9" s="74"/>
       <c r="XFD9" t="s">
@@ -21064,7 +21022,7 @@
       </c>
     </row>
     <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="A10" s="224" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="75" t="s">
@@ -21073,16 +21031,16 @@
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
       <c r="G10" s="71"/>
-      <c r="K10" s="198" t="s">
+      <c r="K10" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="197" t="s">
+      <c r="L10" s="226"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="197"/>
-      <c r="P10" s="197"/>
+      <c r="O10" s="227"/>
+      <c r="P10" s="227"/>
       <c r="R10" s="70"/>
       <c r="S10" s="71"/>
       <c r="XFD10" t="s">
@@ -21090,7 +21048,7 @@
       </c>
     </row>
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="203"/>
+      <c r="A11" s="224"/>
       <c r="B11" s="76" t="s">
         <v>48</v>
       </c>
@@ -21100,21 +21058,21 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
-      <c r="K11" s="198" t="s">
+      <c r="K11" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="198"/>
-      <c r="M11" s="198"/>
-      <c r="N11" s="197" t="s">
+      <c r="L11" s="226"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="227" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="197"/>
-      <c r="P11" s="197"/>
+      <c r="O11" s="227"/>
+      <c r="P11" s="227"/>
       <c r="R11" s="70"/>
       <c r="S11" s="71"/>
     </row>
     <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="203" t="s">
+      <c r="A12" s="224" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -21126,14 +21084,14 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
-      <c r="K12" s="198" t="s">
+      <c r="K12" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="198"/>
-      <c r="M12" s="198"/>
-      <c r="N12" s="197"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="197"/>
+      <c r="L12" s="226"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="227"/>
+      <c r="O12" s="227"/>
+      <c r="P12" s="227"/>
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="XFD12" t="s">
@@ -21141,7 +21099,7 @@
       </c>
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="240"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="64"/>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -21153,11 +21111,11 @@
       </c>
     </row>
     <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="204" t="s">
+      <c r="B14" s="229"/>
+      <c r="C14" s="232" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -21198,9 +21156,9 @@
       </c>
     </row>
     <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="242"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="205"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="233"/>
       <c r="D15" s="86" t="s">
         <v>76</v>
       </c>
@@ -21755,14 +21713,14 @@
       </c>
     </row>
     <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="222" t="s">
+      <c r="A25" s="206" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="249"/>
+      <c r="B25" s="207"/>
+      <c r="C25" s="208"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="243"/>
       <c r="G25" s="135">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
         <v>0</v>
@@ -21829,104 +21787,104 @@
       <c r="H27" s="151"/>
     </row>
     <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="226"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="226"/>
-      <c r="G28" s="226"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="226"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="226"/>
-      <c r="L28" s="227"/>
-      <c r="N28" s="234" t="s">
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="210"/>
+      <c r="K28" s="210"/>
+      <c r="L28" s="211"/>
+      <c r="N28" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="235"/>
+      <c r="O28" s="219"/>
       <c r="P28" s="152">
         <f>I25</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="228"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="229"/>
-      <c r="I29" s="229"/>
-      <c r="J29" s="229"/>
-      <c r="K29" s="229"/>
-      <c r="L29" s="230"/>
-      <c r="N29" s="236" t="s">
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="213"/>
+      <c r="G29" s="213"/>
+      <c r="H29" s="213"/>
+      <c r="I29" s="213"/>
+      <c r="J29" s="213"/>
+      <c r="K29" s="213"/>
+      <c r="L29" s="214"/>
+      <c r="N29" s="220" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="237"/>
+      <c r="O29" s="221"/>
       <c r="P29" s="153">
         <f>L25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="228"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="229"/>
-      <c r="I30" s="229"/>
-      <c r="J30" s="229"/>
-      <c r="K30" s="229"/>
-      <c r="L30" s="230"/>
-      <c r="N30" s="236" t="s">
+      <c r="B30" s="212"/>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="214"/>
+      <c r="N30" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="237"/>
+      <c r="O30" s="221"/>
       <c r="P30" s="154">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="228"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="229"/>
-      <c r="I31" s="229"/>
-      <c r="J31" s="229"/>
-      <c r="K31" s="229"/>
-      <c r="L31" s="230"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="213"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="213"/>
+      <c r="I31" s="213"/>
+      <c r="J31" s="213"/>
+      <c r="K31" s="213"/>
+      <c r="L31" s="214"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="236" t="s">
+      <c r="N31" s="220" t="s">
         <v>88</v>
       </c>
-      <c r="O31" s="237"/>
+      <c r="O31" s="221"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="228"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="230"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="213"/>
+      <c r="I32" s="213"/>
+      <c r="J32" s="213"/>
+      <c r="K32" s="213"/>
+      <c r="L32" s="214"/>
       <c r="M32" s="2"/>
       <c r="N32" s="155" t="s">
         <v>89</v>
@@ -21941,39 +21899,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="228"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="213"/>
+      <c r="G33" s="213"/>
+      <c r="H33" s="213"/>
+      <c r="I33" s="213"/>
+      <c r="J33" s="213"/>
+      <c r="K33" s="213"/>
+      <c r="L33" s="214"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="238" t="s">
+      <c r="N33" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="O33" s="239"/>
+      <c r="O33" s="223"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="231"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="233"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="157"/>
       <c r="N34" s="158" t="s">
         <v>91</v>
@@ -21988,10 +21946,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="216" t="s">
+      <c r="N35" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="O35" s="217"/>
+      <c r="O35" s="201"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
         <v>0</v>
@@ -22001,55 +21959,19 @@
       <c r="B36" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="219"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="221"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="202"/>
+      <c r="F36" s="202"/>
+      <c r="G36" s="202"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="203"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
@@ -22061,6 +21983,42 @@
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0800-000000000000}">
